--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -1188,25 +1188,25 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F20">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>34.88</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>65.12</v>
+        <v>20.93</v>
       </c>
       <c r="I20" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J20">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K20" s="1">
-        <v>65.12</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2766,25 +2766,25 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F20">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>34.88</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>65.12</v>
+        <v>20.93</v>
       </c>
       <c r="I20" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J20">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K20" s="1">
-        <v>65.12</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="21" spans="1:11">

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -555,19 +555,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>82.34999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="H2" s="1">
-        <v>17.65</v>
+        <v>17.14</v>
       </c>
       <c r="I2" s="2">
         <v>6.9</v>
@@ -745,13 +745,13 @@
         <v>2.56</v>
       </c>
       <c r="I7" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -765,19 +765,19 @@
         <v>38</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="I8" s="2">
         <v>8.6</v>
@@ -803,25 +803,25 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>58.97</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>41.03</v>
+        <v>28.21</v>
       </c>
       <c r="I9" s="2">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="J9">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>41.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -838,25 +838,25 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>85.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H10" s="1">
-        <v>14.71</v>
+        <v>2.94</v>
       </c>
       <c r="I10" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -873,25 +873,25 @@
         <v>41</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>78.05</v>
+        <v>87.8</v>
       </c>
       <c r="H11" s="1">
-        <v>21.95</v>
+        <v>12.2</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="J11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>21.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -905,28 +905,28 @@
         <v>39</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>60.98</v>
+        <v>85</v>
       </c>
       <c r="H12" s="1">
-        <v>39.02</v>
+        <v>15</v>
       </c>
       <c r="I12" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>39.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -955,13 +955,13 @@
         <v>2.78</v>
       </c>
       <c r="I13" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1080,28 +1080,28 @@
         <v>39</v>
       </c>
       <c r="D17">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G17" s="1">
-        <v>67.73999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="H17" s="1">
-        <v>32.26</v>
+        <v>26.67</v>
       </c>
       <c r="I17" s="2">
         <v>7</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1165,13 +1165,13 @@
         <v>9.09</v>
       </c>
       <c r="I19" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1188,25 +1188,25 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="1">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>20.93</v>
+        <v>18.6</v>
       </c>
       <c r="I20" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>13.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1220,28 +1220,28 @@
         <v>39</v>
       </c>
       <c r="D21">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E21">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F21">
         <v>8</v>
       </c>
       <c r="G21" s="1">
-        <v>80.95</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>19.05</v>
+        <v>18.6</v>
       </c>
       <c r="I21" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1308,10 +1308,10 @@
         <v>6.3</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1377,25 +1377,28 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1412,22 +1415,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>81.58</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>18.42</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7.6</v>
       </c>
       <c r="J3">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1569,13 +1575,13 @@
         <v>38</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1584,7 +1590,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1604,22 +1610,25 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>56.41</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>43.59</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6.4</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1636,22 +1645,25 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>11.76</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.1</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1668,22 +1680,25 @@
         <v>41</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>12.2</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.1</v>
       </c>
       <c r="J11">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1697,25 +1712,28 @@
         <v>39</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.5</v>
       </c>
       <c r="J12">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1732,22 +1750,25 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I13" s="2">
+        <v>6.3</v>
       </c>
       <c r="J13">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1764,22 +1785,25 @@
         <v>26</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F14">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>53.85</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>46.15</v>
+      </c>
+      <c r="I14" s="2">
+        <v>9.1</v>
       </c>
       <c r="J14">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1796,22 +1820,25 @@
         <v>15</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>40</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9.1</v>
       </c>
       <c r="J15">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1857,25 +1884,28 @@
         <v>39</v>
       </c>
       <c r="D17">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F17">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>56.67</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>43.33</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6.8</v>
       </c>
       <c r="J17">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1892,22 +1922,25 @@
         <v>40</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F18">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6.9</v>
       </c>
       <c r="J18">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1924,22 +1957,25 @@
         <v>44</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>86.36</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>13.64</v>
+      </c>
+      <c r="I19" s="2">
+        <v>7.5</v>
       </c>
       <c r="J19">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1985,13 +2021,13 @@
         <v>39</v>
       </c>
       <c r="D21">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -2000,7 +2036,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -2020,22 +2056,25 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F22">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>88.89</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>11.11</v>
+      </c>
+      <c r="I22" s="2">
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2133,22 +2172,22 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2">
         <v>28</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>82.34999999999999</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1">
-        <v>17.65</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2171,19 +2210,19 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>89.47</v>
+        <v>81.58</v>
       </c>
       <c r="H3" s="1">
-        <v>10.53</v>
+        <v>18.42</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -2323,13 +2362,13 @@
         <v>2.56</v>
       </c>
       <c r="I7" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2343,19 +2382,19 @@
         <v>38</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="I8" s="2">
         <v>8.6</v>
@@ -2393,13 +2432,13 @@
         <v>41.03</v>
       </c>
       <c r="I9" s="2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="J9">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>41.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2416,25 +2455,25 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>14.71</v>
+        <v>11.76</v>
       </c>
       <c r="I10" s="2">
         <v>7.2</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2451,25 +2490,25 @@
         <v>41</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>78.05</v>
+        <v>87.8</v>
       </c>
       <c r="H11" s="1">
-        <v>21.95</v>
+        <v>12.2</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>21.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2483,28 +2522,28 @@
         <v>39</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>60.98</v>
+        <v>80</v>
       </c>
       <c r="H12" s="1">
-        <v>39.02</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J12">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>39.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2521,25 +2560,25 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>97.22</v>
+        <v>83.33</v>
       </c>
       <c r="H13" s="1">
-        <v>2.78</v>
+        <v>16.67</v>
       </c>
       <c r="I13" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2568,7 +2607,7 @@
         <v>46.15</v>
       </c>
       <c r="I14" s="2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J14">
         <v>12</v>
@@ -2603,7 +2642,7 @@
         <v>40</v>
       </c>
       <c r="I15" s="2">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -2658,28 +2697,28 @@
         <v>39</v>
       </c>
       <c r="D17">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1">
-        <v>67.73999999999999</v>
+        <v>60</v>
       </c>
       <c r="H17" s="1">
-        <v>32.26</v>
+        <v>40</v>
       </c>
       <c r="I17" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2696,16 +2735,16 @@
         <v>40</v>
       </c>
       <c r="E18">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1">
-        <v>72.5</v>
+        <v>67.5</v>
       </c>
       <c r="H18" s="1">
-        <v>27.5</v>
+        <v>32.5</v>
       </c>
       <c r="I18" s="2">
         <v>6.9</v>
@@ -2731,25 +2770,25 @@
         <v>44</v>
       </c>
       <c r="E19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1">
-        <v>90.91</v>
+        <v>86.36</v>
       </c>
       <c r="H19" s="1">
-        <v>9.09</v>
+        <v>13.64</v>
       </c>
       <c r="I19" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2766,25 +2805,25 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="1">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>20.93</v>
+        <v>18.6</v>
       </c>
       <c r="I20" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>13.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2798,28 +2837,28 @@
         <v>39</v>
       </c>
       <c r="D21">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E21">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F21">
         <v>8</v>
       </c>
       <c r="G21" s="1">
-        <v>80.95</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>19.05</v>
+        <v>18.6</v>
       </c>
       <c r="I21" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2848,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2886,10 +2925,10 @@
         <v>6.3</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -1855,22 +1855,25 @@
         <v>34</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>32.35</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6.4</v>
       </c>
       <c r="J16">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1887,25 +1890,25 @@
         <v>30</v>
       </c>
       <c r="E17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1">
-        <v>56.67</v>
+        <v>60</v>
       </c>
       <c r="H17" s="1">
-        <v>43.33</v>
+        <v>40</v>
       </c>
       <c r="I17" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1934,13 +1937,13 @@
         <v>35</v>
       </c>
       <c r="I18" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1969,13 +1972,13 @@
         <v>13.64</v>
       </c>
       <c r="I19" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1992,22 +1995,25 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F20">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>74.42</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>25.58</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7.1</v>
       </c>
       <c r="J20">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2024,22 +2030,25 @@
         <v>43</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F21">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>20.93</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2056,25 +2065,25 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
         <v>8</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2091,22 +2100,25 @@
         <v>44</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F23">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>79.55</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>20.45</v>
+      </c>
+      <c r="I23" s="2">
+        <v>7.1</v>
       </c>
       <c r="J23">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>2.27</v>
       </c>
     </row>
   </sheetData>
@@ -2665,19 +2677,19 @@
         <v>34</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G16" s="1">
-        <v>73.53</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>26.47</v>
+        <v>32.35</v>
       </c>
       <c r="I16" s="2">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2735,19 +2747,19 @@
         <v>40</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
-        <v>67.5</v>
+        <v>65</v>
       </c>
       <c r="H18" s="1">
-        <v>32.5</v>
+        <v>35</v>
       </c>
       <c r="I18" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2805,19 +2817,19 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G20" s="1">
-        <v>81.40000000000001</v>
+        <v>74.42</v>
       </c>
       <c r="H20" s="1">
-        <v>18.6</v>
+        <v>25.58</v>
       </c>
       <c r="I20" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2840,19 +2852,19 @@
         <v>43</v>
       </c>
       <c r="E21">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>81.40000000000001</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>18.6</v>
+        <v>20.93</v>
       </c>
       <c r="I21" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2910,19 +2922,19 @@
         <v>44</v>
       </c>
       <c r="E23">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F23">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G23" s="1">
-        <v>70.45</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>29.55</v>
+        <v>18.18</v>
       </c>
       <c r="I23" s="2">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -1482,22 +1482,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1514,22 +1517,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>97.56</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>2.44</v>
+      </c>
+      <c r="I6" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1546,22 +1552,25 @@
         <v>39</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F7">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>97.44</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>2.56</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.6</v>
       </c>
       <c r="J7">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2304,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2327,19 +2336,19 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>97.56</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I6" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2374,7 +2383,7 @@
         <v>2.56</v>
       </c>
       <c r="I7" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -1450,22 +1450,25 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.1</v>
       </c>
       <c r="J4">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1587,22 +1590,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>9.68</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.5</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2054,10 +2060,10 @@
         <v>7</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2109,25 +2115,25 @@
         <v>44</v>
       </c>
       <c r="E23">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="1">
-        <v>79.55</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>20.45</v>
+        <v>18.18</v>
       </c>
       <c r="I23" s="2">
         <v>7.1</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2266,19 +2272,19 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>78.13</v>
+        <v>84.38</v>
       </c>
       <c r="H4" s="1">
-        <v>21.88</v>
+        <v>15.63</v>
       </c>
       <c r="I4" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2406,19 +2412,19 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>87.09999999999999</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>12.9</v>
+        <v>9.68</v>
       </c>
       <c r="I8" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J8">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -1637,13 +1637,13 @@
         <v>43.59</v>
       </c>
       <c r="I9" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1742,13 +1742,13 @@
         <v>20</v>
       </c>
       <c r="I12" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1765,25 +1765,25 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>75</v>
+        <v>83.33</v>
       </c>
       <c r="H13" s="1">
-        <v>25</v>
+        <v>16.67</v>
       </c>
       <c r="I13" s="2">
         <v>6.3</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2447,16 +2447,16 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>58.97</v>
+        <v>56.41</v>
       </c>
       <c r="H9" s="1">
-        <v>41.03</v>
+        <v>43.59</v>
       </c>
       <c r="I9" s="2">
         <v>6.2</v>

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -593,25 +593,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>89.47</v>
+        <v>92.11</v>
       </c>
       <c r="H3" s="1">
-        <v>10.53</v>
+        <v>7.89</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1415,25 +1415,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>81.58</v>
+        <v>86.84</v>
       </c>
       <c r="H3" s="1">
-        <v>18.42</v>
+        <v>13.16</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2237,25 +2237,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>81.58</v>
+        <v>86.84</v>
       </c>
       <c r="H3" s="1">
-        <v>18.42</v>
+        <v>13.16</v>
       </c>
       <c r="I3" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -978,25 +978,25 @@
         <v>26</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>53.85</v>
+        <v>80.77</v>
       </c>
       <c r="H14" s="1">
-        <v>46.15</v>
+        <v>19.23</v>
       </c>
       <c r="I14" s="2">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>46.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1025,13 +1025,13 @@
         <v>40</v>
       </c>
       <c r="I15" s="2">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1800,25 +1800,25 @@
         <v>26</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>53.85</v>
+        <v>69.23</v>
       </c>
       <c r="H14" s="1">
-        <v>46.15</v>
+        <v>30.77</v>
       </c>
       <c r="I14" s="2">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>46.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1835,25 +1835,25 @@
         <v>15</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>60</v>
+        <v>93.33</v>
       </c>
       <c r="H15" s="1">
-        <v>40</v>
+        <v>6.67</v>
       </c>
       <c r="I15" s="2">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2622,25 +2622,25 @@
         <v>26</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>53.85</v>
+        <v>69.23</v>
       </c>
       <c r="H14" s="1">
-        <v>46.15</v>
+        <v>30.77</v>
       </c>
       <c r="I14" s="2">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>46.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2657,25 +2657,25 @@
         <v>15</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>60</v>
+        <v>93.33</v>
       </c>
       <c r="H15" s="1">
-        <v>40</v>
+        <v>6.67</v>
       </c>
       <c r="I15" s="2">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -1625,19 +1625,19 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1">
-        <v>56.41</v>
+        <v>58.97</v>
       </c>
       <c r="H9" s="1">
-        <v>43.59</v>
+        <v>41.03</v>
       </c>
       <c r="I9" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>12.2</v>
       </c>
       <c r="I11" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2447,16 +2447,16 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1">
-        <v>56.41</v>
+        <v>58.97</v>
       </c>
       <c r="H9" s="1">
-        <v>43.59</v>
+        <v>41.03</v>
       </c>
       <c r="I9" s="2">
         <v>6.2</v>

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -2127,7 +2127,7 @@
         <v>18.18</v>
       </c>
       <c r="I23" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -2447,19 +2447,19 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>58.97</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>41.03</v>
+        <v>20.51</v>
       </c>
       <c r="I9" s="2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2482,19 +2482,19 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>88.23999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>11.76</v>
+        <v>14.71</v>
       </c>
       <c r="I10" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2517,19 +2517,19 @@
         <v>41</v>
       </c>
       <c r="E11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>87.8</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>12.2</v>
+        <v>17.07</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2564,7 +2564,7 @@
         <v>20</v>
       </c>
       <c r="I12" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2587,19 +2587,19 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>83.33</v>
+        <v>80.56</v>
       </c>
       <c r="H13" s="1">
-        <v>16.67</v>
+        <v>19.44</v>
       </c>
       <c r="I13" s="2">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>18.18</v>
       </c>
       <c r="I23" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J23">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -2622,19 +2622,19 @@
         <v>26</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>69.23</v>
+        <v>73.08</v>
       </c>
       <c r="H14" s="1">
-        <v>30.77</v>
+        <v>26.92</v>
       </c>
       <c r="I14" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2657,19 +2657,19 @@
         <v>15</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>93.33</v>
+        <v>86.67</v>
       </c>
       <c r="H15" s="1">
-        <v>6.67</v>
+        <v>13.33</v>
       </c>
       <c r="I15" s="2">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -2202,19 +2202,19 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>80</v>
+        <v>82.86</v>
       </c>
       <c r="H2" s="1">
-        <v>20</v>
+        <v>17.14</v>
       </c>
       <c r="I2" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2237,19 +2237,19 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H3" s="1">
-        <v>13.16</v>
+        <v>10.53</v>
       </c>
       <c r="I3" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2272,19 +2272,19 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H4" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="I4" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -2692,19 +2692,19 @@
         <v>34</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G16" s="1">
-        <v>67.65000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="H16" s="1">
-        <v>32.35</v>
+        <v>20.59</v>
       </c>
       <c r="I16" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>30</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H17" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I17" s="2">
         <v>6.9</v>

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -2774,7 +2774,7 @@
         <v>35</v>
       </c>
       <c r="I18" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2797,19 +2797,19 @@
         <v>44</v>
       </c>
       <c r="E19">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>86.36</v>
+        <v>90.91</v>
       </c>
       <c r="H19" s="1">
-        <v>13.64</v>
+        <v>9.09</v>
       </c>
       <c r="I19" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2832,19 +2832,19 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F20">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G20" s="1">
-        <v>74.42</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>25.58</v>
+        <v>18.6</v>
       </c>
       <c r="I20" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2867,19 +2867,19 @@
         <v>43</v>
       </c>
       <c r="E21">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21" s="1">
-        <v>79.06999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>20.93</v>
+        <v>23.26</v>
       </c>
       <c r="I21" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2937,19 +2937,19 @@
         <v>44</v>
       </c>
       <c r="E23">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>81.81999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="H23" s="1">
-        <v>18.18</v>
+        <v>11.36</v>
       </c>
       <c r="I23" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
         <v>0</v>

--- a/academias/Humanidades - Estadisticos 20221.xlsx
+++ b/academias/Humanidades - Estadisticos 20221.xlsx
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         <v>2.44</v>
       </c>
       <c r="I6" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>2.56</v>
       </c>
       <c r="I7" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>9.68</v>
       </c>
       <c r="I8" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>0</v>
